--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb18a1de324a4d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R509f572679a542a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb36a2735c4d841d0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a68bbc462ca48b7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0927f1bdc4c14461"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2707d15da794ac3"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R509f572679a542a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc70248473e8a4282"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a68bbc462ca48b7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R63e1000db4c8496e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2707d15da794ac3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6c64f3fa6cb403c"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc70248473e8a4282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R88d1788ff2394c32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R63e1000db4c8496e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a24871614fd46aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6c64f3fa6cb403c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4480a53ede0945fa"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R88d1788ff2394c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3e1209ffc164f24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6a24871614fd46aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R41bb5797a6804c09"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4480a53ede0945fa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013c54e2e99a41d7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3e1209ffc164f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3e9a981bede4c38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R41bb5797a6804c09"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raf0d472428e1472f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R013c54e2e99a41d7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c117d12f9d4782"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3e9a981bede4c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89649a79ffbd431c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raf0d472428e1472f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf32c98390c804657"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c117d12f9d4782"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f77422239974d36"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89649a79ffbd431c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbede053001894f64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf32c98390c804657"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1260603d56dc42f7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f77422239974d36"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4355caa37944676"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbede053001894f64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R779dd03793814a36"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1260603d56dc42f7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8633887f289d4874"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4355caa37944676"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5254740682214cca"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R779dd03793814a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ce036aecb5f438e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8633887f289d4874"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc8035e7b7e274bce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5254740682214cca"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R394cfcb323434b21"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ce036aecb5f438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R896570e8a9834f6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc8035e7b7e274bce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf5fb2884d5704e94"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R394cfcb323434b21"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R840415063faa46c4"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R896570e8a9834f6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01639b7c4d5443ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf5fb2884d5704e94"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdeb27b2fe6a14b5d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R840415063faa46c4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f767771c1c845fc"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R01639b7c4d5443ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf0114a6ee5774e8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdeb27b2fe6a14b5d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0a4d8581554b4ca6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f767771c1c845fc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R451a0d0281414ec8"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf0114a6ee5774e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22db0c7764ca45d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0a4d8581554b4ca6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64649c67d9744a5c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R451a0d0281414ec8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62d44347338d4933"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ChartColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22db0c7764ca45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc16db33c25a4003"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -180,7 +180,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64649c67d9744a5c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbe1b085c6c084ebd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -237,6 +237,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62d44347338d4933"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb7240fd87547d1"/>
 </x:worksheet>
 </file>